--- a/recipes/onion-garlic-free-indian/focus-states/09-uttarakhand/excel/uttarakhand-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/09-uttarakhand/excel/uttarakhand-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bhatt ki Churkani</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bhatt ki Churkani</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Side  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 15 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1749,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Cook until creamy. Tadka.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel or clay pot — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cook until creamy. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Tadka. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 142  ·  Protein 3 g  ·  Carbs 28 g  ·  Fat 2 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Soya · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Bhatt ki Churkani: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Soya; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1790,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1984,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Palak ka Saag</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Palak ka Saag</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1812,7 +1994,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Side  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1832,44 +2014,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2035,35 +2217,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Wilt, temper.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Wash greens in several changes of water; drain and squeeze dry.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Wilt, temper. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 18  ·  Protein 2 g  ·  Carbs 3 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Wash greens until the water is clear; grit ruins the dish. For Palak ka Saag: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2077,7 +2425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2089,7 +2437,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pahadi Jeera Aloo</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pahadi Jeera Aloo</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2099,7 +2447,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Side  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2119,44 +2467,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2340,36 +2688,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Fry until the edges brown.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Fry until the edges brown. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 79  ·  Protein 2 g  ·  Carbs 17 g  ·  Fat 0 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Pahadi Jeera Aloo: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2383,7 +2897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2395,7 +2909,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Mandua Roti</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Mandua Roti</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2405,7 +2919,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Bread  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2425,44 +2939,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2592,33 +3106,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Pat, cook on iron tawa.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Pat, cook on iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 210  ·  Protein 4 g  ·  Carbs 45 g  ·  Fat 1 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Mandua Roti: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2632,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2644,7 +3311,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Wheat Roti</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Wheat Roti</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2654,7 +3321,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Bread  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2674,44 +3341,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2841,33 +3508,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Phulka on iron.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Phulka on iron. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 318  ·  Protein 9 g  ·  Carbs 54 g  ·  Fat 8 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Wheat Roti: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2881,7 +3701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2893,7 +3713,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bari Roti</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bari Roti</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2903,7 +3723,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Bread  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2923,44 +3743,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3108,34 +3928,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Roll slightly thick, cook on iron.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Roll slightly thick, cook on iron. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 318  ·  Protein 9 g  ·  Carbs 54 g  ·  Fat 8 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Bari Roti: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3149,7 +4122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3161,7 +4134,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bal Mithai</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bal Mithai</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3171,7 +4144,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Sweet  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3191,44 +4164,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -3358,33 +4331,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Cook in steel, cut, roll.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Cook in steel, cut, roll. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 404  ·  Protein 7 g  ·  Carbs 62 g  ·  Fat 13 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Bal Mithai: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3398,7 +4524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3410,7 +4536,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Arsa</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Arsa</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3420,7 +4546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Sweet  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3440,44 +4566,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 30 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3625,34 +4751,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Pat discs, fry on medium.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Pat discs, fry on medium. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 423  ·  Protein 4 g  ·  Carbs 80 g  ·  Fat 10 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Arsa: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3666,7 +4945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3678,7 +4957,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Singodi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Singodi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3688,7 +4967,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Sweet  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3708,44 +4987,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3875,33 +5154,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Cook, set small cones.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Cook, set small cones. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 308  ·  Protein 7 g  ·  Carbs 38 g  ·  Fat 13 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Singodi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3915,7 +5347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3927,7 +5359,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Jhangora Kheer</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Jhangora Kheer</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3937,7 +5369,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Dessert  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3957,44 +5389,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 10 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -4160,35 +5592,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Simmer in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Simmer in steel. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 311  ·  Protein 10 g  ·  Carbs 46 g  ·  Fat 11 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Jhangora Kheer: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4466,7 +6051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4478,7 +6063,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rice Kheer</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rice Kheer</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4488,7 +6073,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Dessert  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4508,44 +6093,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 10 min · Cook 35 min</t>
         </is>
       </c>
     </row>
@@ -4693,34 +6278,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Simmer in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Simmer in steel. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 437  ·  Protein 12 g  ·  Carbs 77 g  ·  Fat 9 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Rice Kheer: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4734,7 +6472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4746,7 +6484,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Fruit Raita Sweet</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Fruit Raita Sweet</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4756,7 +6494,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Dessert  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4776,44 +6514,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -4979,35 +6717,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Fold. No onion raita.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Fold. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>No onion raita. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 101  ·  Protein 3 g  ·  Carbs 20 g  ·  Fat 2 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Fruit Raita Sweet: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve in a steel or glass bowl. Stir at the pass so it is not split or settled. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5021,7 +6925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5033,7 +6937,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Cucumber Lemon Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Cucumber Lemon Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5043,7 +6947,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Salad  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5063,44 +6967,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>Prep 6 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5248,34 +7152,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Toss.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 16  ·  Protein 1 g  ·  Carbs 4 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Cucumber Lemon Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5289,7 +7346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5301,7 +7358,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Mooli Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Mooli Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5311,7 +7368,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Salad  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5331,44 +7388,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5534,35 +7591,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Toss. No onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>No onion. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 67  ·  Protein 2 g  ·  Carbs 10 g  ·  Fat 2 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Mooli Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5576,7 +7799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5588,7 +7811,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Tomato Ginger Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Tomato Ginger Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5598,7 +7821,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Salad  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5618,44 +7841,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>Prep 6 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5803,34 +8026,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Toss.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 14  ·  Protein 1 g  ·  Carbs 3 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Tomato Ginger Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8907,7 +11283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8919,7 +11295,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Aloo ke Gutke</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Aloo ke Gutke</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8929,7 +11305,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Starter  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8949,44 +11325,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -9224,39 +11600,205 @@
       <c r="C24" s="46" t="n"/>
       <c r="D24" s="46" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Crisp potatoes in mustard oil with jakhiya.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Crisp potatoes in mustard oil with jakhiya. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 950  ·  Protein 0 g  ·  Carbs 1 g  ·  Fat 107 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Aloo ke Gutke: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="33">
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9270,7 +11812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9282,7 +11824,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Jhangora Tikki</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Jhangora Tikki</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9292,7 +11834,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Starter  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9312,44 +11854,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9515,35 +12057,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Shape, pan-fry on iron.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Shape, pan-fry on iron. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 211  ·  Protein 5 g  ·  Carbs 27 g  ·  Fat 10 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Jhangora Tikki: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9557,7 +12252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9569,7 +12264,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Garhwali Kapa Bites</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Garhwali Kapa Bites</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9579,7 +12274,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Starter  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9599,44 +12294,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9838,37 +12533,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Cook a thick kadhi in steel. Serve with toasted roti strips.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cook a thick kadhi in steel. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Serve with toasted roti strips. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 182  ·  Protein 10 g  ·  Carbs 26 g  ·  Fat 4 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Garhwali Kapa Bites: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9882,7 +12756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9894,7 +12768,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kafuli</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kafuli</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9904,7 +12778,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Main  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9924,44 +12798,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -10199,39 +13073,205 @@
       <c r="C24" s="46" t="n"/>
       <c r="D24" s="46" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Cook greens, mash, thicken, tadka.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Wash greens in several changes of water; drain and squeeze dry.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Cook greens, mash, thicken, tadka. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 190  ·  Protein 4 g  ·  Carbs 26 g  ·  Fat 8 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Wash greens until the water is clear; grit ruins the dish. For Kafuli: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="33">
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10245,7 +13285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10257,7 +13297,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Phaanu</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Phaanu</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10267,7 +13307,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Main  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10287,44 +13327,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>65 min</t>
+          <t>Prep 20 min · Cook 45 min</t>
         </is>
       </c>
     </row>
@@ -10544,38 +13584,243 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Cook dals very soft. Rice paste. Long simmer. Ghee tadka.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel or clay pot — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cook dals very soft. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Rice paste. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Long simmer. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Ghee tadka. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>kcal 335  ·  Protein 13 g  ·  Carbs 51 g  ·  Fat 8 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>For Phaanu: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="35">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10589,7 +13834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10601,7 +13846,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chainsoo</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chainsoo</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10611,7 +13856,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Uttarakhand kitchen  ·  Main  ·  Kumaoni and Garhwali vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Uttarakhand  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10631,44 +13876,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 15 min · Cook 35 min</t>
         </is>
       </c>
     </row>
@@ -10870,37 +14115,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Roast dal, grind, cook with water and spices until thick and smoky.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="66" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Roast dal, grind, cook with water and spices until thick and smoky. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 113  ·  Protein 3 g  ·  Carbs 9 g  ·  Fat 7 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Chainsoo: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
